--- a/data/trans_orig/P6604-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6604-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a posiciones dolorosas/ fatigantes en su trabajo en 2007</t>
+          <t>Población según la exposición a posiciones dolorosas/ fatigantes en su trabajo en 2007 (tasa de respuesta: 99,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89173</t>
+          <t>91181</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>125580</t>
+          <t>123627</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51202</t>
+          <t>51022</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>74527</t>
+          <t>76613</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>148550</t>
+          <t>147148</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>192127</t>
+          <t>191891</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,57%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>95972</t>
+          <t>96394</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>134187</t>
+          <t>134450</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39863</t>
+          <t>37966</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63925</t>
+          <t>62941</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>144411</t>
+          <t>143921</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>188120</t>
+          <t>186309</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,54%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>76685</t>
+          <t>76783</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>110115</t>
+          <t>110814</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19148</t>
+          <t>18868</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39091</t>
+          <t>37946</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>104089</t>
+          <t>100732</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>140436</t>
+          <t>140440</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53927</t>
+          <t>53998</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>84739</t>
+          <t>84557</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9398</t>
+          <t>9465</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23707</t>
+          <t>24271</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68504</t>
+          <t>68910</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>103879</t>
+          <t>102991</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,09%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>160610</t>
+          <t>163772</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>209692</t>
+          <t>210170</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>130259</t>
+          <t>129560</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>163686</t>
+          <t>163619</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>304838</t>
+          <t>303986</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>362824</t>
+          <t>364855</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>44,14%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>106095</t>
+          <t>104985</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>144986</t>
+          <t>145480</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44924</t>
+          <t>45154</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71214</t>
+          <t>72461</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>160395</t>
+          <t>157618</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>206549</t>
+          <t>207069</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,05%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>109574</t>
+          <t>110617</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>152626</t>
+          <t>149330</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25259</t>
+          <t>25640</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47108</t>
+          <t>48429</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>142407</t>
+          <t>141545</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>189203</t>
+          <t>188966</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,86%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>99639</t>
+          <t>100836</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>141004</t>
+          <t>142328</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17520</t>
+          <t>17291</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>37688</t>
+          <t>38419</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>126286</t>
+          <t>124700</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>170632</t>
+          <t>169705</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,53%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>113927</t>
+          <t>109451</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>150791</t>
+          <t>150710</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>85390</t>
+          <t>85999</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>114561</t>
+          <t>114619</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>207363</t>
+          <t>205661</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>253483</t>
+          <t>255080</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>41,25%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>81956</t>
+          <t>81933</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>118475</t>
+          <t>117402</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>44476</t>
+          <t>44853</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>70978</t>
+          <t>70699</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>136315</t>
+          <t>135548</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>180135</t>
+          <t>177622</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>28,72%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>85797</t>
+          <t>84602</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>121009</t>
+          <t>121671</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25474</t>
+          <t>24722</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47305</t>
+          <t>46031</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>116351</t>
+          <t>118810</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>159793</t>
+          <t>159653</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,82%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>58933</t>
+          <t>59215</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>92983</t>
+          <t>91505</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12243</t>
+          <t>12684</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31809</t>
+          <t>30854</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>76991</t>
+          <t>76500</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>114733</t>
+          <t>114831</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,57%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>197693</t>
+          <t>198082</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>242358</t>
+          <t>243613</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>186804</t>
+          <t>185961</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>227421</t>
+          <t>226364</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>396994</t>
+          <t>397285</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>458959</t>
+          <t>457387</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,5%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>119983</t>
+          <t>120322</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>161279</t>
+          <t>160682</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>64775</t>
+          <t>65401</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>96125</t>
+          <t>97138</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>191638</t>
+          <t>196609</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>246655</t>
+          <t>249545</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,46%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>97343</t>
+          <t>100614</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>136391</t>
+          <t>139164</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>47131</t>
+          <t>46289</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>76643</t>
+          <t>74582</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>154352</t>
+          <t>154857</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>201520</t>
+          <t>204194</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,65%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>62124</t>
+          <t>63181</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>95523</t>
+          <t>94800</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30097</t>
+          <t>30396</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55992</t>
+          <t>55330</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>99680</t>
+          <t>98192</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>142746</t>
+          <t>140961</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>600557</t>
+          <t>602254</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>690631</t>
+          <t>688464</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>481078</t>
+          <t>483932</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>545069</t>
+          <t>547522</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1109667</t>
+          <t>1107108</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1218523</t>
+          <t>1216345</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,55%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>439205</t>
+          <t>441566</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>519056</t>
+          <t>518544</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>219701</t>
+          <t>222249</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>275125</t>
+          <t>280601</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>677476</t>
+          <t>674026</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>772576</t>
+          <t>770085</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,3%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>404107</t>
+          <t>406469</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>479676</t>
+          <t>481169</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>134253</t>
+          <t>135537</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>181528</t>
+          <t>179670</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>557155</t>
+          <t>554188</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>645972</t>
+          <t>642956</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,96%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>303552</t>
+          <t>305309</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>374229</t>
+          <t>377636</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>86435</t>
+          <t>85746</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>125350</t>
+          <t>127083</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>401560</t>
+          <t>405199</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>485815</t>
+          <t>487862</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,66%</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a posiciones dolorosas/ fatigantes en su trabajo en 2012</t>
+          <t>Población según la exposición a posiciones dolorosas/ fatigantes en su trabajo en 2012 (tasa de respuesta: 99,1%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52330</t>
+          <t>52469</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82765</t>
+          <t>82169</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38953</t>
+          <t>39675</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62040</t>
+          <t>63763</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>98565</t>
+          <t>98895</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>137414</t>
+          <t>136911</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,9%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>85774</t>
+          <t>85986</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>118906</t>
+          <t>118313</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51955</t>
+          <t>50437</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>76250</t>
+          <t>75639</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>144745</t>
+          <t>144035</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>185729</t>
+          <t>183194</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>42,68%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49006</t>
+          <t>49152</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>75624</t>
+          <t>78285</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23281</t>
+          <t>23462</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45786</t>
+          <t>47110</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>77103</t>
+          <t>78997</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>114406</t>
+          <t>113583</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,46%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27945</t>
+          <t>26939</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50075</t>
+          <t>50102</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22745</t>
+          <t>23410</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38555</t>
+          <t>39608</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65908</t>
+          <t>66231</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,43%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>108576</t>
+          <t>108040</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>147465</t>
+          <t>148611</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>82911</t>
+          <t>83566</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>116485</t>
+          <t>116150</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>200603</t>
+          <t>198651</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>250761</t>
+          <t>251743</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,95%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>113950</t>
+          <t>111859</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>152635</t>
+          <t>152199</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>82686</t>
+          <t>82542</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>114624</t>
+          <t>115529</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>206618</t>
+          <t>207167</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>257007</t>
+          <t>257830</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,85%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75931</t>
+          <t>75102</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>108837</t>
+          <t>110172</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40206</t>
+          <t>40619</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>67719</t>
+          <t>66929</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>124395</t>
+          <t>121290</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>168999</t>
+          <t>166826</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,49%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>45837</t>
+          <t>44914</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>74219</t>
+          <t>75805</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13665</t>
+          <t>13588</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>32595</t>
+          <t>32387</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>64415</t>
+          <t>65485</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>101363</t>
+          <t>101454</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,89%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>79664</t>
+          <t>77821</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>114394</t>
+          <t>114261</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60846</t>
+          <t>60409</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>90750</t>
+          <t>90931</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>147655</t>
+          <t>146613</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>194687</t>
+          <t>193510</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,18%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>91260</t>
+          <t>90540</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>126289</t>
+          <t>125855</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>61866</t>
+          <t>60415</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>91892</t>
+          <t>90247</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>158922</t>
+          <t>160084</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>207621</t>
+          <t>205611</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,45%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>69073</t>
+          <t>70673</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>103042</t>
+          <t>105252</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29046</t>
+          <t>29361</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54029</t>
+          <t>55206</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>108670</t>
+          <t>108673</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>151002</t>
+          <t>147692</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>27,62%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20559</t>
+          <t>19795</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42884</t>
+          <t>43224</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13700</t>
+          <t>14161</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33262</t>
+          <t>32813</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40310</t>
+          <t>38834</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>70259</t>
+          <t>68475</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>140100</t>
+          <t>141244</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>181775</t>
+          <t>182167</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>106920</t>
+          <t>108310</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>141504</t>
+          <t>141785</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>258434</t>
+          <t>261323</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>313286</t>
+          <t>313996</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,95%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>100532</t>
+          <t>101476</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>136688</t>
+          <t>137184</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>84356</t>
+          <t>84348</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>116139</t>
+          <t>117045</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>193532</t>
+          <t>196020</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>247376</t>
+          <t>243966</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,15%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>85667</t>
+          <t>83841</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>120627</t>
+          <t>119351</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>33590</t>
+          <t>34686</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>59392</t>
+          <t>60660</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>129663</t>
+          <t>125709</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>175276</t>
+          <t>170387</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>23,85%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23057</t>
+          <t>22700</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44695</t>
+          <t>46456</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19239</t>
+          <t>18837</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39659</t>
+          <t>39158</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>47056</t>
+          <t>46434</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>79395</t>
+          <t>78566</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,0%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>417918</t>
+          <t>415026</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>488840</t>
+          <t>489560</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>318009</t>
+          <t>316986</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>380195</t>
+          <t>381273</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>748952</t>
+          <t>755882</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>843883</t>
+          <t>849398</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>36,0%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>422344</t>
+          <t>426619</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>495950</t>
+          <t>498239</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>308614</t>
+          <t>307849</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>367890</t>
+          <t>369425</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>749202</t>
+          <t>752289</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>845678</t>
+          <t>845115</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,82%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>310818</t>
+          <t>307993</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>375888</t>
+          <t>375945</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>148330</t>
+          <t>148483</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>199411</t>
+          <t>199067</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>472575</t>
+          <t>473065</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>557884</t>
+          <t>557290</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,62%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>136137</t>
+          <t>134955</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>186036</t>
+          <t>186337</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>69479</t>
+          <t>71251</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>105743</t>
+          <t>106106</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>214981</t>
+          <t>216903</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>277110</t>
+          <t>278223</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,79%</t>
         </is>
       </c>
     </row>
@@ -6692,7 +6692,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a posiciones dolorosas/ fatigantes en su trabajo en 2016</t>
+          <t>Población según la exposición a posiciones dolorosas/ fatigantes en su trabajo en 2016 (tasa de respuesta: 99,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>61322</t>
+          <t>59675</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>89216</t>
+          <t>87543</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>54381</t>
+          <t>55278</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>78421</t>
+          <t>79549</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>120241</t>
+          <t>121591</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>159071</t>
+          <t>159208</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,96%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65538</t>
+          <t>66271</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>94970</t>
+          <t>95099</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41189</t>
+          <t>40554</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65312</t>
+          <t>64203</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>113984</t>
+          <t>113733</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>150779</t>
+          <t>149895</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,69%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44486</t>
+          <t>45162</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>71359</t>
+          <t>70591</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19062</t>
+          <t>18895</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38308</t>
+          <t>37889</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>70090</t>
+          <t>68345</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>102257</t>
+          <t>100873</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,69%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21838</t>
+          <t>22059</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41960</t>
+          <t>43207</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13824</t>
+          <t>14359</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31969</t>
+          <t>31724</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39523</t>
+          <t>39025</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>67968</t>
+          <t>66958</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,39%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>112109</t>
+          <t>112240</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>151706</t>
+          <t>151293</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>89233</t>
+          <t>89119</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>121833</t>
+          <t>121250</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>211322</t>
+          <t>210374</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>264595</t>
+          <t>261983</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,35%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>110473</t>
+          <t>109382</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>149910</t>
+          <t>149936</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>71265</t>
+          <t>71560</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>102672</t>
+          <t>103484</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>188688</t>
+          <t>191472</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>240883</t>
+          <t>240447</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,19%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79186</t>
+          <t>80506</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>114232</t>
+          <t>116180</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47864</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>73722</t>
+          <t>74965</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>136080</t>
+          <t>134669</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>180337</t>
+          <t>180348</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,7 +7767,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40016</t>
+          <t>39756</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>68023</t>
+          <t>68369</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12936</t>
+          <t>12588</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31952</t>
+          <t>31400</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>58107</t>
+          <t>57867</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>90791</t>
+          <t>91611</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,41%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>58552</t>
+          <t>57769</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>90658</t>
+          <t>88310</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>58952</t>
+          <t>60046</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>87967</t>
+          <t>88381</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>124739</t>
+          <t>125117</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>167249</t>
+          <t>168999</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,69%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>118342</t>
+          <t>118615</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>156137</t>
+          <t>155889</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>78274</t>
+          <t>79045</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>109595</t>
+          <t>109525</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>207357</t>
+          <t>207676</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>257828</t>
+          <t>259295</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,95%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>66426</t>
+          <t>66129</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>99124</t>
+          <t>100255</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50922</t>
+          <t>52145</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>80243</t>
+          <t>80187</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>126126</t>
+          <t>126564</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>170492</t>
+          <t>168913</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,67%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>55598</t>
+          <t>57316</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86765</t>
+          <t>87194</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28531</t>
+          <t>28212</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>51820</t>
+          <t>49932</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>91645</t>
+          <t>92439</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>130444</t>
+          <t>131173</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,71%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>143829</t>
+          <t>144233</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>182066</t>
+          <t>183705</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>135655</t>
+          <t>134418</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>172027</t>
+          <t>171743</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>287941</t>
+          <t>287956</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>343022</t>
+          <t>343104</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,52%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>95583</t>
+          <t>95833</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>131988</t>
+          <t>132886</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>71213</t>
+          <t>71209</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>103091</t>
+          <t>104167</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>175287</t>
+          <t>176895</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>224636</t>
+          <t>226824</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,42%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>70066</t>
+          <t>69993</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>103513</t>
+          <t>101472</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>44236</t>
+          <t>44219</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>72372</t>
+          <t>73178</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8875,7 +8875,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>121748</t>
+          <t>123503</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>166493</t>
+          <t>167118</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,15%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24737</t>
+          <t>24997</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48738</t>
+          <t>47879</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18457</t>
+          <t>18982</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39110</t>
+          <t>39588</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>49134</t>
+          <t>48988</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>81128</t>
+          <t>80456</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>409050</t>
+          <t>405689</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>478492</t>
+          <t>478814</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>363854</t>
+          <t>362977</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>426971</t>
+          <t>427148</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>789737</t>
+          <t>787409</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>885412</t>
+          <t>884385</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,14%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>420213</t>
+          <t>425765</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>492850</t>
+          <t>493743</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>290338</t>
+          <t>286378</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>349148</t>
+          <t>347670</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>734639</t>
+          <t>731193</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>828019</t>
+          <t>822095</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,6%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>288971</t>
+          <t>288646</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>353048</t>
+          <t>356029</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>184187</t>
+          <t>184054</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>237965</t>
+          <t>235417</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>487798</t>
+          <t>492763</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>570836</t>
+          <t>575362</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,51%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>165299</t>
+          <t>165396</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>216462</t>
+          <t>216262</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>90605</t>
+          <t>93235</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>130677</t>
+          <t>132727</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>266313</t>
+          <t>269676</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>333804</t>
+          <t>339871</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,89%</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9769,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a posiciones dolorosas/ fatigantes en su trabajo en 2023</t>
+          <t>Población según la exposición a posiciones dolorosas/ fatigantes en su trabajo en 2023 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9964,12 +9964,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28800</t>
+          <t>28402</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54649</t>
+          <t>57083</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9979,12 +9979,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19493</t>
+          <t>19123</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36304</t>
+          <t>36723</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53053</t>
+          <t>50737</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84926</t>
+          <t>84225</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,4%</t>
         </is>
       </c>
     </row>
@@ -10077,12 +10077,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48858</t>
+          <t>49081</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>79214</t>
+          <t>78840</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39561</t>
+          <t>40414</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57928</t>
+          <t>58833</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>96178</t>
+          <t>94531</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>130008</t>
+          <t>129156</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>43,56%</t>
         </is>
       </c>
     </row>
@@ -10190,12 +10190,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25663</t>
+          <t>26605</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>48241</t>
+          <t>48073</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22760</t>
+          <t>22478</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38257</t>
+          <t>38553</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>53307</t>
+          <t>51961</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>81244</t>
+          <t>80099</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,01%</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10303,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20836</t>
+          <t>21113</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49750</t>
+          <t>47648</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12193</t>
+          <t>12677</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27333</t>
+          <t>26898</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38789</t>
+          <t>38678</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68145</t>
+          <t>69233</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,35%</t>
         </is>
       </c>
     </row>
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>146827</t>
+          <t>142284</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>472492</t>
+          <t>466083</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>50440</t>
+          <t>50389</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>73001</t>
+          <t>73130</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>208040</t>
+          <t>206908</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>599207</t>
+          <t>588982</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>79,03%</t>
         </is>
       </c>
     </row>
@@ -10646,12 +10646,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34738</t>
+          <t>36001</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>192225</t>
+          <t>194695</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>68577</t>
+          <t>68093</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>93241</t>
+          <t>93129</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64834</t>
+          <t>74516</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>277835</t>
+          <t>277517</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,24%</t>
         </is>
       </c>
     </row>
@@ -10759,12 +10759,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25981</t>
+          <t>28347</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>159254</t>
+          <t>160977</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10774,12 +10774,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32131</t>
+          <t>31604</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50236</t>
+          <t>51082</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>49922</t>
+          <t>54899</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>194125</t>
+          <t>194704</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,13%</t>
         </is>
       </c>
     </row>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8304</t>
+          <t>7913</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59589</t>
+          <t>62135</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13951</t>
+          <t>14925</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29902</t>
+          <t>31192</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>17579</t>
+          <t>19194</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>82370</t>
+          <t>82723</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -11102,12 +11102,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>42212</t>
+          <t>40529</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>68416</t>
+          <t>67914</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11117,12 +11117,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21923</t>
+          <t>23168</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>58206</t>
+          <t>59522</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11152,12 +11152,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>65639</t>
+          <t>67010</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>117024</t>
+          <t>117414</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,81%</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11215,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>47457</t>
+          <t>47382</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>76244</t>
+          <t>75169</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11230,12 +11230,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21862</t>
+          <t>21896</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>58291</t>
+          <t>58912</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11265,12 +11265,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>71367</t>
+          <t>74285</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>124630</t>
+          <t>125517</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11300,12 +11300,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,21%</t>
         </is>
       </c>
     </row>
@@ -11328,12 +11328,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24433</t>
+          <t>23704</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46845</t>
+          <t>46425</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16991</t>
+          <t>18621</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48215</t>
+          <t>49152</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11378,12 +11378,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47497</t>
+          <t>50017</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>85470</t>
+          <t>87039</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11413,12 +11413,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,8%</t>
         </is>
       </c>
     </row>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13825</t>
+          <t>14006</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35276</t>
+          <t>35563</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10871</t>
+          <t>10829</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>99295</t>
+          <t>99700</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11491,12 +11491,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32793</t>
+          <t>32407</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>153821</t>
+          <t>147970</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>43,86%</t>
         </is>
       </c>
     </row>
@@ -11671,12 +11671,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>80496</t>
+          <t>79908</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>111270</t>
+          <t>110881</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11686,12 +11686,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>66567</t>
+          <t>68568</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>91861</t>
+          <t>91655</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>154560</t>
+          <t>151274</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>195498</t>
+          <t>192618</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11756,12 +11756,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>46,54%</t>
         </is>
       </c>
     </row>
@@ -11784,12 +11784,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>56896</t>
+          <t>57593</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>87856</t>
+          <t>86158</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>47230</t>
+          <t>47707</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>69921</t>
+          <t>69991</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>110835</t>
+          <t>111316</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>148471</t>
+          <t>147751</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,7%</t>
         </is>
       </c>
     </row>
@@ -11897,12 +11897,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>23426</t>
+          <t>22633</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>46208</t>
+          <t>47032</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11912,12 +11912,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>22888</t>
+          <t>22591</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>41135</t>
+          <t>40304</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11947,12 +11947,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>51411</t>
+          <t>50828</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>80149</t>
+          <t>80348</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,42%</t>
         </is>
       </c>
     </row>
@@ -12010,12 +12010,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17790</t>
+          <t>18197</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39133</t>
+          <t>38488</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12025,12 +12025,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13237</t>
+          <t>13381</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27270</t>
+          <t>27200</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12060,12 +12060,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>34926</t>
+          <t>35119</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>60387</t>
+          <t>59491</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12095,12 +12095,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -12240,12 +12240,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>337600</t>
+          <t>342948</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>793249</t>
+          <t>768428</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12255,12 +12255,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>179351</t>
+          <t>174847</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>234186</t>
+          <t>232794</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12290,12 +12290,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>544531</t>
+          <t>542508</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1092781</t>
+          <t>1122045</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12325,12 +12325,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>62,58%</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>153861</t>
+          <t>167139</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>391210</t>
+          <t>390560</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12368,12 +12368,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>196215</t>
+          <t>187727</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>255421</t>
+          <t>254768</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>341942</t>
+          <t>336461</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>626090</t>
+          <t>628025</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,03%</t>
         </is>
       </c>
     </row>
@@ -12466,12 +12466,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>101843</t>
+          <t>101393</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>252378</t>
+          <t>249458</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12481,12 +12481,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>114464</t>
+          <t>114467</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>157202</t>
+          <t>157517</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12521,7 +12521,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>215646</t>
+          <t>206928</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>386566</t>
+          <t>394308</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12551,12 +12551,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,99%</t>
         </is>
       </c>
     </row>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>56998</t>
+          <t>57994</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>153042</t>
+          <t>152430</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12594,12 +12594,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>69052</t>
+          <t>68074</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>190835</t>
+          <t>234541</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>141537</t>
+          <t>139414</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>301712</t>
+          <t>304019</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,96%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6604-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6604-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>91181</t>
+          <t>88772</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>123627</t>
+          <t>126057</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51022</t>
+          <t>49853</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>76613</t>
+          <t>75308</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>147148</t>
+          <t>147958</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>191891</t>
+          <t>191844</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,56%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>96394</t>
+          <t>97279</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>134450</t>
+          <t>134181</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37966</t>
+          <t>39075</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62941</t>
+          <t>62733</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>143921</t>
+          <t>144984</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>186309</t>
+          <t>187710</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,79%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>76783</t>
+          <t>76531</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>110814</t>
+          <t>111131</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18868</t>
+          <t>18878</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37946</t>
+          <t>38021</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>100732</t>
+          <t>103224</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>140440</t>
+          <t>142183</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,36%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53998</t>
+          <t>52582</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>84557</t>
+          <t>82776</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9465</t>
+          <t>9987</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24271</t>
+          <t>24364</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68910</t>
+          <t>67331</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>102991</t>
+          <t>102744</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,05%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>163772</t>
+          <t>162477</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>210170</t>
+          <t>210114</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>129560</t>
+          <t>129661</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>163619</t>
+          <t>162651</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>303986</t>
+          <t>301692</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>364855</t>
+          <t>359420</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>43,48%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>104985</t>
+          <t>106112</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>145480</t>
+          <t>146533</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45154</t>
+          <t>45417</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72461</t>
+          <t>74875</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>157618</t>
+          <t>159344</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>207069</t>
+          <t>209891</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,39%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>110617</t>
+          <t>109712</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>149330</t>
+          <t>148690</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25640</t>
+          <t>26372</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48429</t>
+          <t>48414</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>141545</t>
+          <t>143195</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>188966</t>
+          <t>186764</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,59%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>100836</t>
+          <t>99691</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>142328</t>
+          <t>141961</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17291</t>
+          <t>17907</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>38419</t>
+          <t>39265</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>124700</t>
+          <t>125446</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>169705</t>
+          <t>170024</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,57%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>109451</t>
+          <t>110683</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>150710</t>
+          <t>149379</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>85999</t>
+          <t>85748</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>114619</t>
+          <t>115694</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>205661</t>
+          <t>207024</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>255080</t>
+          <t>259441</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,95%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>81933</t>
+          <t>82048</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>117402</t>
+          <t>119082</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>44853</t>
+          <t>46034</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>70699</t>
+          <t>72491</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>135548</t>
+          <t>134374</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>177622</t>
+          <t>178565</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,87%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>84602</t>
+          <t>85319</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>121671</t>
+          <t>123482</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24722</t>
+          <t>24718</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46031</t>
+          <t>46174</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>118810</t>
+          <t>115339</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>159653</t>
+          <t>157723</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,5%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>59215</t>
+          <t>59082</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>91505</t>
+          <t>91857</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12684</t>
+          <t>12399</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30854</t>
+          <t>31096</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>76500</t>
+          <t>75633</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>114831</t>
+          <t>115231</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,63%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>198082</t>
+          <t>197036</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>243613</t>
+          <t>244875</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>185961</t>
+          <t>185728</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>226364</t>
+          <t>224392</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>397285</t>
+          <t>394863</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>457387</t>
+          <t>459252</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,69%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>120322</t>
+          <t>120036</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>160682</t>
+          <t>159561</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>65401</t>
+          <t>64248</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>97138</t>
+          <t>96852</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>196609</t>
+          <t>194529</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>249545</t>
+          <t>245758</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,06%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>100614</t>
+          <t>99736</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>139164</t>
+          <t>137921</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>46289</t>
+          <t>45345</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>74582</t>
+          <t>76412</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>154857</t>
+          <t>157773</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>204194</t>
+          <t>206036</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,85%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>63181</t>
+          <t>60366</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>94800</t>
+          <t>94050</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30396</t>
+          <t>31138</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55330</t>
+          <t>56252</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>98192</t>
+          <t>100717</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>140961</t>
+          <t>139919</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>602254</t>
+          <t>602828</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>688464</t>
+          <t>683821</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>483932</t>
+          <t>481205</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>547522</t>
+          <t>546429</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1107108</t>
+          <t>1107970</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1216345</t>
+          <t>1210341</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>41,34%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>441566</t>
+          <t>438626</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>518544</t>
+          <t>516804</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>222249</t>
+          <t>218595</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>280601</t>
+          <t>274512</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>674026</t>
+          <t>676440</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>770085</t>
+          <t>769372</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,28%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>406469</t>
+          <t>406485</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>481169</t>
+          <t>484731</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>135537</t>
+          <t>135152</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>179670</t>
+          <t>183117</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>554188</t>
+          <t>558690</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>642956</t>
+          <t>648174</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,14%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>305309</t>
+          <t>302615</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>377636</t>
+          <t>372817</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>85746</t>
+          <t>85399</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>127083</t>
+          <t>127055</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>405199</t>
+          <t>402619</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>487862</t>
+          <t>481466</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,45%</t>
         </is>
       </c>
     </row>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52469</t>
+          <t>53270</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82169</t>
+          <t>83628</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39675</t>
+          <t>39041</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63763</t>
+          <t>64812</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>98895</t>
+          <t>97890</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>136911</t>
+          <t>136758</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,86%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>85986</t>
+          <t>86423</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>118313</t>
+          <t>118726</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50437</t>
+          <t>48927</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>75639</t>
+          <t>75870</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>144035</t>
+          <t>144215</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>183194</t>
+          <t>185697</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>43,27%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49152</t>
+          <t>48553</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>78285</t>
+          <t>75893</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23462</t>
+          <t>22625</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47110</t>
+          <t>45633</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>78997</t>
+          <t>78866</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>113583</t>
+          <t>113326</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,4%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26939</t>
+          <t>27889</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50102</t>
+          <t>50150</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>8076</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23410</t>
+          <t>22497</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39608</t>
+          <t>39809</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66231</t>
+          <t>67398</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,7%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>108040</t>
+          <t>106831</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>148611</t>
+          <t>148080</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>83566</t>
+          <t>82653</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>116150</t>
+          <t>115125</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>198651</t>
+          <t>200175</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>251743</t>
+          <t>253723</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,24%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>111859</t>
+          <t>112891</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>152199</t>
+          <t>152566</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>82542</t>
+          <t>81698</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>115529</t>
+          <t>113976</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>207167</t>
+          <t>206870</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>257830</t>
+          <t>256265</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,62%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75102</t>
+          <t>74831</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>110172</t>
+          <t>111472</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40619</t>
+          <t>41406</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>66929</t>
+          <t>68954</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>121290</t>
+          <t>124060</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>166826</t>
+          <t>169330</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,85%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>44914</t>
+          <t>44764</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>75805</t>
+          <t>74310</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13588</t>
+          <t>13302</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>32387</t>
+          <t>31987</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>65485</t>
+          <t>63663</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>101454</t>
+          <t>100245</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>77821</t>
+          <t>78325</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>114261</t>
+          <t>113572</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60409</t>
+          <t>60293</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>90931</t>
+          <t>90483</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>146613</t>
+          <t>148558</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>193510</t>
+          <t>196218</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,69%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>90540</t>
+          <t>90270</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>125855</t>
+          <t>126516</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>60415</t>
+          <t>60106</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>90247</t>
+          <t>89882</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>160084</t>
+          <t>159579</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>205611</t>
+          <t>210144</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>39,29%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>70673</t>
+          <t>69847</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>105252</t>
+          <t>104541</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29361</t>
+          <t>29192</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55206</t>
+          <t>53083</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>108673</t>
+          <t>107332</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>147692</t>
+          <t>150607</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>28,16%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19795</t>
+          <t>20409</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43224</t>
+          <t>42200</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14161</t>
+          <t>14348</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32813</t>
+          <t>34508</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38834</t>
+          <t>37828</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>68475</t>
+          <t>68510</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,81%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>141244</t>
+          <t>142075</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>182167</t>
+          <t>181943</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>108310</t>
+          <t>107020</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>141785</t>
+          <t>142568</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>261323</t>
+          <t>258572</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>313996</t>
+          <t>314516</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>44,03%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>101476</t>
+          <t>98924</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>137184</t>
+          <t>136445</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>84348</t>
+          <t>84996</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>117045</t>
+          <t>118429</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>196020</t>
+          <t>195438</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>243966</t>
+          <t>246681</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,53%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>83841</t>
+          <t>84919</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>119351</t>
+          <t>122024</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>34686</t>
+          <t>34135</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>60660</t>
+          <t>58969</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>125709</t>
+          <t>126126</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>170387</t>
+          <t>171934</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,07%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22700</t>
+          <t>22742</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46456</t>
+          <t>47287</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18837</t>
+          <t>18838</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39158</t>
+          <t>38932</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>46434</t>
+          <t>45946</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>78566</t>
+          <t>79131</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>415026</t>
+          <t>420175</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>489560</t>
+          <t>491943</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>316986</t>
+          <t>317144</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>381273</t>
+          <t>377751</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>755882</t>
+          <t>754551</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>849398</t>
+          <t>848554</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>35,96%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>426619</t>
+          <t>424875</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>498239</t>
+          <t>496273</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>307849</t>
+          <t>307863</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>369425</t>
+          <t>369900</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>752289</t>
+          <t>746669</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>845115</t>
+          <t>846700</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,88%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>307993</t>
+          <t>309045</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>375945</t>
+          <t>377511</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>148483</t>
+          <t>148223</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>199067</t>
+          <t>198081</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>473065</t>
+          <t>472467</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>557290</t>
+          <t>555166</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,53%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>134955</t>
+          <t>137626</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>186337</t>
+          <t>189932</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>71251</t>
+          <t>70067</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>106106</t>
+          <t>104676</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>216903</t>
+          <t>217612</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>278223</t>
+          <t>278442</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>59675</t>
+          <t>60489</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>87543</t>
+          <t>87860</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>55278</t>
+          <t>54525</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>79549</t>
+          <t>78106</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>121591</t>
+          <t>121158</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>159208</t>
+          <t>157968</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>38,66%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66271</t>
+          <t>66653</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>95099</t>
+          <t>94637</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40554</t>
+          <t>40636</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64203</t>
+          <t>63388</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>113733</t>
+          <t>112616</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>149895</t>
+          <t>148823</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,42%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>45162</t>
+          <t>45450</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>70591</t>
+          <t>71252</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18895</t>
+          <t>18636</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37889</t>
+          <t>37447</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>68345</t>
+          <t>69462</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>100873</t>
+          <t>103896</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>25,43%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22059</t>
+          <t>20209</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43207</t>
+          <t>43156</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14359</t>
+          <t>13903</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31724</t>
+          <t>33747</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39025</t>
+          <t>39954</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66958</t>
+          <t>68332</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,72%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>112240</t>
+          <t>112748</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>151293</t>
+          <t>151678</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>89119</t>
+          <t>88336</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>121250</t>
+          <t>120434</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>210374</t>
+          <t>209554</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>261983</t>
+          <t>262910</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,48%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>109382</t>
+          <t>111606</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>149936</t>
+          <t>150838</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>71560</t>
+          <t>72152</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>103484</t>
+          <t>102975</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>191472</t>
+          <t>192213</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>240447</t>
+          <t>239705</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,09%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80506</t>
+          <t>79171</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>116180</t>
+          <t>113914</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>47203</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74965</t>
+          <t>74520</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>134669</t>
+          <t>134993</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>180348</t>
+          <t>180282</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,39%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39756</t>
+          <t>39301</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>68369</t>
+          <t>67164</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12588</t>
+          <t>14308</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31400</t>
+          <t>33921</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>57867</t>
+          <t>58486</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>91611</t>
+          <t>91570</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57769</t>
+          <t>58527</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>88310</t>
+          <t>88578</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60046</t>
+          <t>59444</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>88381</t>
+          <t>89515</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>125117</t>
+          <t>122750</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>168999</t>
+          <t>165235</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,09%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>118615</t>
+          <t>118644</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>155889</t>
+          <t>157383</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>79045</t>
+          <t>78828</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>109525</t>
+          <t>109613</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>207676</t>
+          <t>206646</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>259295</t>
+          <t>256243</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,46%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>66129</t>
+          <t>65957</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>100255</t>
+          <t>100270</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52145</t>
+          <t>50949</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>80187</t>
+          <t>80409</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>126564</t>
+          <t>124358</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>168913</t>
+          <t>167055</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,38%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>57316</t>
+          <t>55804</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>87194</t>
+          <t>87768</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28212</t>
+          <t>28249</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>49932</t>
+          <t>51814</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>92439</t>
+          <t>92040</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>131173</t>
+          <t>130399</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,59%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>144233</t>
+          <t>144061</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>183705</t>
+          <t>182363</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>134418</t>
+          <t>133563</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>171743</t>
+          <t>170353</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>287956</t>
+          <t>286801</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>343104</t>
+          <t>340512</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,16%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>95833</t>
+          <t>97055</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>132886</t>
+          <t>131134</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>71209</t>
+          <t>71862</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>104167</t>
+          <t>103534</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>176895</t>
+          <t>175267</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>226824</t>
+          <t>223534</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>30,96%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>69993</t>
+          <t>69860</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>101472</t>
+          <t>102276</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>44219</t>
+          <t>44817</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>73178</t>
+          <t>72948</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>123503</t>
+          <t>120781</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>167118</t>
+          <t>165504</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,92%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24997</t>
+          <t>24402</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47879</t>
+          <t>47118</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18982</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39588</t>
+          <t>40329</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>48988</t>
+          <t>49243</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>80456</t>
+          <t>79877</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>405689</t>
+          <t>406415</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>478814</t>
+          <t>478315</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>362977</t>
+          <t>364761</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>427148</t>
+          <t>430727</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>787409</t>
+          <t>787368</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>884385</t>
+          <t>885787</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,2%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>425765</t>
+          <t>426945</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>493743</t>
+          <t>497770</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>286378</t>
+          <t>288784</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>347670</t>
+          <t>349743</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>731193</t>
+          <t>733185</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>822095</t>
+          <t>824797</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,71%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>288646</t>
+          <t>291288</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>356029</t>
+          <t>355038</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>184054</t>
+          <t>186638</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>235417</t>
+          <t>238675</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>492763</t>
+          <t>489553</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>575362</t>
+          <t>575347</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>165396</t>
+          <t>166095</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>216262</t>
+          <t>219391</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>93235</t>
+          <t>91460</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>132727</t>
+          <t>132812</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>269676</t>
+          <t>268728</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>339871</t>
+          <t>335934</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>
@@ -9959,32 +9959,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>40423</t>
+          <t>44880</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28402</t>
+          <t>32788</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57083</t>
+          <t>61160</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9994,32 +9994,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>26369</t>
+          <t>28208</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19123</t>
+          <t>20362</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36723</t>
+          <t>39060</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10029,32 +10029,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>66792</t>
+          <t>73088</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50737</t>
+          <t>58526</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84225</t>
+          <t>93003</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,11%</t>
         </is>
       </c>
     </row>
@@ -10072,32 +10072,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>62518</t>
+          <t>66835</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49081</t>
+          <t>52824</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>78840</t>
+          <t>83017</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10107,32 +10107,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>49148</t>
+          <t>53791</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40414</t>
+          <t>43710</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58833</t>
+          <t>63936</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10142,32 +10142,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>111665</t>
+          <t>120627</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>94531</t>
+          <t>101325</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>129156</t>
+          <t>137934</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>41,69%</t>
         </is>
       </c>
     </row>
@@ -10185,32 +10185,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>36473</t>
+          <t>43910</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26605</t>
+          <t>31363</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>48073</t>
+          <t>57240</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10220,32 +10220,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>29783</t>
+          <t>31781</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22478</t>
+          <t>23612</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38553</t>
+          <t>41088</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10255,32 +10255,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>66256</t>
+          <t>75691</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>51961</t>
+          <t>60759</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>80099</t>
+          <t>92097</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,84%</t>
         </is>
       </c>
     </row>
@@ -10298,32 +10298,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32758</t>
+          <t>37842</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21113</t>
+          <t>24648</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47648</t>
+          <t>55769</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10333,32 +10333,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19056</t>
+          <t>23588</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12677</t>
+          <t>16132</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26898</t>
+          <t>33985</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10368,32 +10368,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>51814</t>
+          <t>61430</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38678</t>
+          <t>46261</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69233</t>
+          <t>79906</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>24,15%</t>
         </is>
       </c>
     </row>
@@ -10411,17 +10411,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>172171</t>
+          <t>193467</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>172171</t>
+          <t>193467</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>172171</t>
+          <t>193467</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10446,17 +10446,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>124356</t>
+          <t>137369</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>124356</t>
+          <t>137369</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>124356</t>
+          <t>137369</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10481,17 +10481,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>296527</t>
+          <t>330836</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>296527</t>
+          <t>330836</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>296527</t>
+          <t>330836</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10528,32 +10528,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>329400</t>
+          <t>96112</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>142284</t>
+          <t>79307</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>466083</t>
+          <t>116747</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10563,32 +10563,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>60597</t>
+          <t>65851</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>50389</t>
+          <t>55178</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>73130</t>
+          <t>79330</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10598,32 +10598,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>389997</t>
+          <t>161963</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>206908</t>
+          <t>138432</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>588982</t>
+          <t>184080</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>33,23%</t>
         </is>
       </c>
     </row>
@@ -10641,32 +10641,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>100456</t>
+          <t>108235</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36001</t>
+          <t>92021</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>194695</t>
+          <t>129411</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10676,32 +10676,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>80049</t>
+          <t>87545</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>68093</t>
+          <t>76542</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>93129</t>
+          <t>101879</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10711,32 +10711,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>180505</t>
+          <t>195780</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>74516</t>
+          <t>170891</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>277517</t>
+          <t>219009</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>39,53%</t>
         </is>
       </c>
     </row>
@@ -10754,32 +10754,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>83031</t>
+          <t>92443</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28347</t>
+          <t>74425</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>160977</t>
+          <t>111475</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10789,32 +10789,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>40809</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31604</t>
+          <t>34371</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51082</t>
+          <t>55216</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10824,32 +10824,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>123841</t>
+          <t>136729</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>54899</t>
+          <t>116940</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>194704</t>
+          <t>159082</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>28,72%</t>
         </is>
       </c>
     </row>
@@ -10867,32 +10867,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>29716</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7913</t>
+          <t>24144</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>62135</t>
+          <t>51762</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10902,32 +10902,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21167</t>
+          <t>22994</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14925</t>
+          <t>15956</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31192</t>
+          <t>33935</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10937,32 +10937,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>50883</t>
+          <t>59497</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19194</t>
+          <t>46155</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>82723</t>
+          <t>78797</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>14,22%</t>
         </is>
       </c>
     </row>
@@ -10980,17 +10980,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>542603</t>
+          <t>333292</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>542603</t>
+          <t>333292</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>542603</t>
+          <t>333292</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11015,17 +11015,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>202623</t>
+          <t>220677</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>202623</t>
+          <t>220677</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>202623</t>
+          <t>220677</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11050,17 +11050,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>745227</t>
+          <t>553968</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>745227</t>
+          <t>553968</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>745227</t>
+          <t>553968</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11097,32 +11097,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>53929</t>
+          <t>60402</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>40529</t>
+          <t>47185</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>67914</t>
+          <t>74444</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11132,32 +11132,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>42994</t>
+          <t>50445</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23168</t>
+          <t>40105</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>59522</t>
+          <t>60450</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11167,32 +11167,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>96923</t>
+          <t>110847</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>67010</t>
+          <t>93285</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>117414</t>
+          <t>129733</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>36,34%</t>
         </is>
       </c>
     </row>
@@ -11210,32 +11210,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>61248</t>
+          <t>64809</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>47382</t>
+          <t>49692</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>75169</t>
+          <t>82840</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11245,32 +11245,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>43172</t>
+          <t>50334</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21896</t>
+          <t>40199</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>58912</t>
+          <t>60815</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11280,32 +11280,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>104420</t>
+          <t>115142</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>74285</t>
+          <t>96203</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>125517</t>
+          <t>133028</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,26%</t>
         </is>
       </c>
     </row>
@@ -11323,32 +11323,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>34268</t>
+          <t>43095</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23704</t>
+          <t>30526</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46425</t>
+          <t>57831</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11358,32 +11358,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>35095</t>
+          <t>40927</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18621</t>
+          <t>31960</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>49152</t>
+          <t>51092</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11393,32 +11393,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>69363</t>
+          <t>84022</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>50017</t>
+          <t>68324</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>87039</t>
+          <t>103709</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>29,05%</t>
         </is>
       </c>
     </row>
@@ -11436,32 +11436,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>22991</t>
+          <t>35073</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14006</t>
+          <t>22863</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35563</t>
+          <t>52116</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11471,32 +11471,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>43650</t>
+          <t>11962</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10829</t>
+          <t>6956</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>99700</t>
+          <t>19362</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11506,32 +11506,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>66641</t>
+          <t>47035</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32407</t>
+          <t>33636</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>147970</t>
+          <t>65501</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>18,35%</t>
         </is>
       </c>
     </row>
@@ -11549,17 +11549,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>172436</t>
+          <t>203379</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>172436</t>
+          <t>203379</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>172436</t>
+          <t>203379</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11584,17 +11584,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>164911</t>
+          <t>153667</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>164911</t>
+          <t>153667</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>164911</t>
+          <t>153667</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11619,17 +11619,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>337347</t>
+          <t>357046</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>337347</t>
+          <t>357046</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>337347</t>
+          <t>357046</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11666,32 +11666,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>94870</t>
+          <t>107293</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>79908</t>
+          <t>90251</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>110881</t>
+          <t>123344</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11701,32 +11701,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>79571</t>
+          <t>88533</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>68568</t>
+          <t>76187</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>91655</t>
+          <t>100934</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11736,32 +11736,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>174440</t>
+          <t>195827</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>151274</t>
+          <t>176702</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>192618</t>
+          <t>215407</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>47,16%</t>
         </is>
       </c>
     </row>
@@ -11779,32 +11779,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>70776</t>
+          <t>71865</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>57593</t>
+          <t>56626</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>86158</t>
+          <t>87543</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11814,32 +11814,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>58302</t>
+          <t>61219</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>47707</t>
+          <t>49906</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>69991</t>
+          <t>72434</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11849,32 +11849,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>129078</t>
+          <t>133084</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>111316</t>
+          <t>114924</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>147751</t>
+          <t>153073</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>33,51%</t>
         </is>
       </c>
     </row>
@@ -11892,32 +11892,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>33536</t>
+          <t>37586</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>22633</t>
+          <t>26597</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>47032</t>
+          <t>50749</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11927,32 +11927,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>30906</t>
+          <t>36966</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>22591</t>
+          <t>28058</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>40304</t>
+          <t>49049</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11962,32 +11962,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>64442</t>
+          <t>74551</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>50828</t>
+          <t>58921</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>80348</t>
+          <t>91717</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>20,08%</t>
         </is>
       </c>
     </row>
@@ -12005,32 +12005,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>26604</t>
+          <t>31374</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18197</t>
+          <t>21280</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38488</t>
+          <t>44703</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12040,32 +12040,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>19275</t>
+          <t>21947</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13381</t>
+          <t>15271</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27200</t>
+          <t>30346</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12075,32 +12075,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>45879</t>
+          <t>53322</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>35119</t>
+          <t>41297</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>59491</t>
+          <t>69693</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>15,26%</t>
         </is>
       </c>
     </row>
@@ -12118,17 +12118,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>225786</t>
+          <t>248119</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>225786</t>
+          <t>248119</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>225786</t>
+          <t>248119</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12153,17 +12153,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>188054</t>
+          <t>208665</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>188054</t>
+          <t>208665</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>188054</t>
+          <t>208665</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12188,17 +12188,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>413840</t>
+          <t>456784</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>413840</t>
+          <t>456784</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>413840</t>
+          <t>456784</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12235,32 +12235,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>518622</t>
+          <t>308687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>342948</t>
+          <t>277346</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>768428</t>
+          <t>340400</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12270,32 +12270,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>209531</t>
+          <t>233038</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>174847</t>
+          <t>210398</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>232794</t>
+          <t>254550</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12305,32 +12305,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>728153</t>
+          <t>541724</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>542508</t>
+          <t>505403</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1122045</t>
+          <t>583490</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>34,35%</t>
         </is>
       </c>
     </row>
@@ -12348,32 +12348,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>294998</t>
+          <t>311744</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>167139</t>
+          <t>278549</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>390560</t>
+          <t>344291</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12383,32 +12383,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>230671</t>
+          <t>252889</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>187727</t>
+          <t>232485</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>254768</t>
+          <t>276022</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12418,32 +12418,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>525668</t>
+          <t>564633</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>336461</t>
+          <t>526020</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>628025</t>
+          <t>604814</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,61%</t>
         </is>
       </c>
     </row>
@@ -12461,32 +12461,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>187308</t>
+          <t>217034</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>101393</t>
+          <t>185717</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>249458</t>
+          <t>247828</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12496,32 +12496,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>136594</t>
+          <t>153960</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>114467</t>
+          <t>133086</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>157517</t>
+          <t>174423</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12531,32 +12531,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>323902</t>
+          <t>370994</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>206928</t>
+          <t>335289</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>394308</t>
+          <t>405241</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>23,86%</t>
         </is>
       </c>
     </row>
@@ -12574,32 +12574,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>112069</t>
+          <t>140792</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>57994</t>
+          <t>112023</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>152430</t>
+          <t>165903</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12609,32 +12609,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>103149</t>
+          <t>80492</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>68074</t>
+          <t>66254</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>234541</t>
+          <t>95586</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12644,32 +12644,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>215218</t>
+          <t>221284</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>139414</t>
+          <t>193211</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>304019</t>
+          <t>256825</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>15,12%</t>
         </is>
       </c>
     </row>
@@ -12687,17 +12687,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1112997</t>
+          <t>978257</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1112997</t>
+          <t>978257</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1112997</t>
+          <t>978257</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12722,17 +12722,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>679944</t>
+          <t>720378</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>679944</t>
+          <t>720378</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>679944</t>
+          <t>720378</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12757,17 +12757,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1792941</t>
+          <t>1698635</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1792941</t>
+          <t>1698635</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1792941</t>
+          <t>1698635</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
